--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260922.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260922.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.29%</t>
+          <t>10.05%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.08%</t>
+          <t>9.25%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.13%</t>
+          <t>7.95%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.24%</t>
+          <t>7.83%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>7.10%</t>
+          <t>6.95%</t>
         </is>
       </c>
     </row>
@@ -726,139 +726,139 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.09%</t>
+          <t>5.04%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>89,118,000</t>
+          <t>25,107,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>4.94%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2,544,000</t>
+          <t>89,118,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>4.91%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>24,987,000</t>
+          <t>7,420,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.87%</t>
+          <t>4.86%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>7,240,000</t>
+          <t>2,544,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>4.68%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>5,656,561</t>
+          <t>6,464,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>4.26%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>6,464,000</t>
+          <t>5,582,561</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>4.16%</t>
+          <t>4.07%</t>
         </is>
       </c>
     </row>
@@ -880,51 +880,51 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.90%</t>
+          <t>4.01%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>4,280,848</t>
+          <t>9,037,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>3.63%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>9,037,000</t>
+          <t>3,943,848</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.35%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>5,546,000</t>
+          <t>5,696,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
@@ -1056,29 +1056,29 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>6,628,000</t>
+          <t>3,543,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
@@ -1095,34 +1095,34 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>446,000</t>
+          <t>400,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2,712,000</t>
+          <t>5,182,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>1,234,000</t>
+          <t>1,363,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.24%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.17%</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1371,12 +1371,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,12 +1481,12 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>8,634,645,119</t>
+          <t>6,735,506,642</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>2,131,572,797</t>
+          <t>2,154,930,397</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>757,766,663</t>
+          <t>1,352,553,765</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>1,670,236,766</t>
+          <t>3,061,265,369</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr"/>
